--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtika\OneDrive\Desktop\AI-Powered Business Anomaly Detection &amp; Alert System\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtika\OneDrive\Desktop\AI-Powered Business Anomaly Detection &amp; Alert System\AI-Powered-Business-Anomaly-Detection-Alert-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4ED8391E-E2E3-4C00-AE51-1E737FA66DC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674B871F-5E84-4727-9F8B-108396B69DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD6EBFFE-96D3-4723-B053-0A171988F675}"/>
   </bookViews>
@@ -895,7 +895,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B6E15561-A3FA-43C7-A38E-77E72BB9C370}">
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G18"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.33203125" bestFit="1" customWidth="1"/>
@@ -963,7 +963,7 @@
         <v>5080</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E16" si="0">(C3/D3)*100</f>
+        <f t="shared" ref="E3:E17" si="0">(C3/D3)*100</f>
         <v>3.3858267716535431</v>
       </c>
       <c r="F3" s="2">
@@ -1283,6 +1283,54 @@
       </c>
       <c r="G16" s="2">
         <v>3000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="1">
+        <v>46250</v>
+      </c>
+      <c r="B17" s="2">
+        <v>144400</v>
+      </c>
+      <c r="C17">
+        <v>65</v>
+      </c>
+      <c r="D17" s="2">
+        <v>9571</v>
+      </c>
+      <c r="E17" s="3">
+        <f>(C17/D17)*100</f>
+        <v>0.67913488663671506</v>
+      </c>
+      <c r="F17" s="2">
+        <v>48500</v>
+      </c>
+      <c r="G17" s="2">
+        <v>4250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="1">
+        <v>46251</v>
+      </c>
+      <c r="B18" s="2">
+        <v>17745</v>
+      </c>
+      <c r="C18">
+        <v>127</v>
+      </c>
+      <c r="D18" s="2">
+        <v>4000</v>
+      </c>
+      <c r="E18" s="3">
+        <f>(C18/D18)*100</f>
+        <v>3.1749999999999998</v>
+      </c>
+      <c r="F18" s="2">
+        <v>47000</v>
+      </c>
+      <c r="G18" s="2">
+        <v>3500</v>
       </c>
     </row>
   </sheetData>

--- a/Dataset.xlsx
+++ b/Dataset.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gtika\OneDrive\Desktop\AI-Powered Business Anomaly Detection &amp; Alert System\AI-Powered-Business-Anomaly-Detection-Alert-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{674B871F-5E84-4727-9F8B-108396B69DE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D44F844-68B4-4871-9FB4-AF842A564C14}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{CD6EBFFE-96D3-4723-B053-0A171988F675}"/>
   </bookViews>
@@ -963,7 +963,7 @@
         <v>5080</v>
       </c>
       <c r="E3" s="3">
-        <f t="shared" ref="E3:E17" si="0">(C3/D3)*100</f>
+        <f t="shared" ref="E3:E16" si="0">(C3/D3)*100</f>
         <v>3.3858267716535431</v>
       </c>
       <c r="F3" s="2">
@@ -981,14 +981,14 @@
         <v>87800</v>
       </c>
       <c r="C4">
-        <v>178</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2">
         <v>5160</v>
       </c>
       <c r="E4" s="3">
         <f t="shared" si="0"/>
-        <v>3.4496124031007755</v>
+        <v>2.0155038759689923</v>
       </c>
       <c r="F4" s="2">
         <v>44200</v>
@@ -1002,23 +1002,23 @@
         <v>46238</v>
       </c>
       <c r="B5" s="2">
-        <v>55400</v>
+        <v>89600</v>
       </c>
       <c r="C5">
-        <v>104</v>
+        <v>180</v>
       </c>
       <c r="D5" s="2">
         <v>5240</v>
       </c>
       <c r="E5" s="3">
         <f t="shared" si="0"/>
-        <v>1.9847328244274809</v>
+        <v>3.4351145038167941</v>
       </c>
       <c r="F5" s="2">
         <v>43900</v>
       </c>
       <c r="G5" s="2">
-        <v>5800</v>
+        <v>2500</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1122,23 +1122,23 @@
         <v>46243</v>
       </c>
       <c r="B10" s="2">
-        <v>61200</v>
+        <v>17000</v>
       </c>
       <c r="C10">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="D10" s="2">
         <v>5620</v>
       </c>
       <c r="E10" s="3">
         <f t="shared" si="0"/>
-        <v>2.2241992882562278</v>
+        <v>2.0284697508896796</v>
       </c>
       <c r="F10" s="2">
         <v>48600</v>
       </c>
       <c r="G10" s="2">
-        <v>6700</v>
+        <v>2400</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1218,23 +1218,23 @@
         <v>46247</v>
       </c>
       <c r="B14" s="2">
-        <v>69500</v>
+        <v>115500</v>
       </c>
       <c r="C14">
-        <v>95</v>
+        <v>213</v>
       </c>
       <c r="D14" s="2">
         <v>5920</v>
       </c>
       <c r="E14" s="3">
         <f t="shared" si="0"/>
-        <v>1.6047297297297296</v>
+        <v>3.5979729729729728</v>
       </c>
       <c r="F14" s="2">
         <v>52200</v>
       </c>
       <c r="G14" s="2">
-        <v>7400</v>
+        <v>2940</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1314,17 +1314,17 @@
         <v>46251</v>
       </c>
       <c r="B18" s="2">
-        <v>17745</v>
+        <v>128000</v>
       </c>
       <c r="C18">
-        <v>127</v>
+        <v>185</v>
       </c>
       <c r="D18" s="2">
         <v>4000</v>
       </c>
       <c r="E18" s="3">
         <f>(C18/D18)*100</f>
-        <v>3.1749999999999998</v>
+        <v>4.625</v>
       </c>
       <c r="F18" s="2">
         <v>47000</v>
